--- a/data/geologie_template.xlsx
+++ b/data/geologie_template.xlsx
@@ -4134,7 +4134,7 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2024-07-24 09:00:01.658569</t>
+    <t>2024-07-24 09:03:32.553435</t>
   </si>
   <si>
     <t>version</t>
